--- a/src/xlsx/buildingsA.xlsx
+++ b/src/xlsx/buildingsA.xlsx
@@ -820,6 +820,7 @@
       <c r="J8" s="1" t="n"/>
       <c r="K8" s="1" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -2598,6 +2599,7 @@
       </c>
       <c r="K64" s="1" t="n"/>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
@@ -2713,6 +2715,7 @@
       <c r="G69" s="1" t="n"/>
       <c r="O69" s="1" t="n"/>
     </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
@@ -2816,6 +2819,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -3501,6 +3505,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -4132,6 +4137,7 @@
       </c>
       <c r="K116" s="1" t="n"/>
     </row>
+    <row r="117"/>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
@@ -4609,6 +4615,7 @@
       </c>
       <c r="K131" s="1" t="n"/>
     </row>
+    <row r="132"/>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
@@ -5930,6 +5937,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -9513,6 +9521,7 @@
       <c r="J56" s="1" t="n"/>
       <c r="K56" s="1" t="n"/>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
@@ -10153,6 +10162,7 @@
       </c>
       <c r="K77" s="1" t="n"/>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -11500,6 +11510,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -12912,6 +12923,7 @@
       </c>
       <c r="K57" s="1" t="n"/>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -14160,6 +14172,7 @@
       </c>
       <c r="K97" s="1" t="n"/>
     </row>
+    <row r="98"/>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
@@ -17775,6 +17788,7 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
@@ -24718,6 +24732,7 @@
       </c>
       <c r="O5" s="1" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -24929,6 +24944,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -25043,6 +25059,7 @@
       </c>
       <c r="O19" s="1" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -25143,6 +25160,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -26401,6 +26419,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -29169,6 +29188,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -31797,6 +31817,7 @@
       <c r="J28" s="1" t="n"/>
       <c r="K28" s="1" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -33395,6 +33416,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -34573,6 +34595,7 @@
       </c>
       <c r="G21" s="1" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -37026,6 +37049,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -38898,6 +38922,7 @@
       </c>
       <c r="O52" s="1" t="n"/>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -39761,6 +39786,7 @@
       <c r="J80" s="1" t="n"/>
       <c r="K80" s="1" t="n"/>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -40080,6 +40106,7 @@
         </is>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -40360,6 +40387,7 @@
       </c>
       <c r="K99" s="1" t="n"/>
     </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
@@ -40978,6 +41006,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -41284,6 +41313,7 @@
       <c r="G17" s="1" t="n"/>
       <c r="O17" s="1" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -41422,6 +41452,7 @@
       </c>
       <c r="O23" s="1" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -42331,6 +42362,7 @@
       <c r="J53" s="1" t="n"/>
       <c r="K53" s="1" t="n"/>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -43011,6 +43043,7 @@
       </c>
       <c r="K75" s="1" t="n"/>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -45256,6 +45289,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -46786,6 +46820,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
@@ -46817,6 +46852,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -47042,6 +47078,7 @@
       </c>
       <c r="K41" s="1" t="n"/>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -47287,6 +47324,7 @@
       <c r="J49" s="1" t="n"/>
       <c r="K49" s="1" t="n"/>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -48760,6 +48798,7 @@
       <c r="J18" s="1" t="n"/>
       <c r="K18" s="1" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -48954,6 +48993,7 @@
       <c r="J25" s="1" t="n"/>
       <c r="K25" s="1" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -50721,6 +50761,7 @@
       </c>
       <c r="K25" s="1" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -50977,6 +51018,7 @@
       <c r="J33" s="1" t="n"/>
       <c r="K33" s="1" t="n"/>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -51249,6 +51291,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -51463,6 +51506,7 @@
       <c r="J48" s="1" t="n"/>
       <c r="K48" s="1" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -51687,6 +51731,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
@@ -51896,6 +51941,7 @@
       <c r="J63" s="1" t="n"/>
       <c r="K63" s="1" t="n"/>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>

--- a/src/xlsx/buildingsA.xlsx
+++ b/src/xlsx/buildingsA.xlsx
@@ -1179,7 +1179,7 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>打不贏你麼。</t>
+          <t>打不贏你嗎。</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>行李已滿了！</t>
+          <t>背包已滿了！</t>
         </is>
       </c>
       <c r="I52" s="1" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>我釣到的魚喲！</t>
+          <t>看看我釣到的魚！</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>好想再去那裡玩兒啊！</t>
+          <t>好想再去那裡玩啊！</t>
         </is>
       </c>
       <c r="I102" s="1" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>道高一尺魔高一丈麼。</t>
+          <t>道高一尺，魔高一丈啊。</t>
         </is>
       </c>
       <c r="I29" s="1" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>啊！輸了麼。</t>
+          <t>啊！輸了嗎。</t>
         </is>
       </c>
       <c r="I41" s="1" t="inlineStr">
@@ -27362,7 +27362,7 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>這麼黑的地方瞎轉悠。</t>
+          <t>這麼黑的地方亂晃。</t>
         </is>
       </c>
       <c r="I15" s="1" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>打不贏你麼。</t>
+          <t>打不贏你嗎。</t>
         </is>
       </c>
       <c r="I58" s="1" t="inlineStr">
@@ -32177,7 +32177,7 @@
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>唔！暴露了麼。</t>
+          <t>唔！被看穿了嗎。</t>
         </is>
       </c>
       <c r="I41" s="1" t="inlineStr">
@@ -37485,7 +37485,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>估計他們說的人是你吧？</t>
+          <t>看來他們說的人是你吧？</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
@@ -37847,7 +37847,7 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>在這附近溜達！</t>
+          <t>在這附近閒晃！</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>哎喲……好噁心！</t>
+          <t>嗚……好想吐！</t>
         </is>
       </c>
       <c r="I14" s="1" t="inlineStr">
@@ -49533,7 +49533,7 @@
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>大意了麼。</t>
+          <t>我太大意了。</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -51584,7 +51584,7 @@
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>估計客人們又會抱怨</t>
+          <t>客人們大概又會抱怨</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
